--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,6 +135,12 @@
       <color rgb="00002060"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -212,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,6 +287,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2509,7 +2518,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3317,7 +3326,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3379,7 +3388,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4179,7 +4188,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4591,7 +4600,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4653,34 +4662,34 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>8475000</v>
+        <v>7712200</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>24637</v>
+        <v>22419</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>7712250</v>
+        <v>7712200</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>22419</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4777,7 +4786,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4901,7 +4910,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4963,7 +4972,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -5437,7 +5446,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5763,7 +5772,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -6035,7 +6044,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6159,7 +6168,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6221,7 +6230,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6345,7 +6354,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6477,7 +6486,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6539,7 +6548,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6811,7 +6820,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7315,7 +7324,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7579,7 +7588,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7703,7 +7712,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7951,7 +7960,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8075,7 +8084,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8471,7 +8480,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8851,7 +8860,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8913,34 +8922,34 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>9286000</v>
+        <v>8635900</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>23810</v>
+        <v>22143</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="5" t="n">
-        <v>8450260</v>
+        <v>8635900</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>21667</v>
+        <v>22143</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -9570,7 +9579,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9627,7 +9636,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9829,7 +9838,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9891,7 +9900,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10015,7 +10024,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10201,7 +10210,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10263,7 +10272,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10457,34 +10466,34 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>8040000</v>
+        <v>7477200</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>23787</v>
+        <v>22122</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>7316400</v>
+        <v>7477200</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>21646</v>
+        <v>22122</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -11535,7 +11544,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -12381,7 +12390,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12448,7 +12457,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12753,7 +12762,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12947,7 +12956,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13009,7 +13018,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13443,7 +13452,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13505,34 +13514,34 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>8806000</v>
+        <v>8013400</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>22294</v>
+        <v>20287</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>8013460</v>
+        <v>8013400</v>
       </c>
       <c r="L198" s="5" t="n">
         <v>20287</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13567,7 +13576,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13629,34 +13638,34 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>7779000</v>
+        <v>7078800</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>23015</v>
+        <v>20943</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>7078890</v>
+        <v>7078800</v>
       </c>
       <c r="L200" s="5" t="n">
         <v>20943</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -14195,7 +14204,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14257,7 +14266,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14629,7 +14638,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14761,34 +14770,34 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
-        <v>8666000</v>
+        <v>8059300</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>21939</v>
+        <v>20403</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K218" s="5" t="n">
-        <v>7886060</v>
+        <v>8059300</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>19965</v>
+        <v>20403</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -14823,7 +14832,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -14885,23 +14894,23 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>7680000</v>
+        <v>6988800</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>22722</v>
+        <v>20677</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K220" s="5" t="n">
@@ -14912,7 +14921,7 @@
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -15327,7 +15336,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15451,7 +15460,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15513,34 +15522,34 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
-        <v>7642000</v>
+        <v>6954200</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>22609</v>
+        <v>20575</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K230" s="5" t="n">
-        <v>6954220</v>
+        <v>6954200</v>
       </c>
       <c r="L230" s="5" t="n">
         <v>20575</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -15575,23 +15584,23 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>7706000</v>
+        <v>7012400</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>22598</v>
+        <v>20564</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
@@ -15602,7 +15611,7 @@
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -16071,7 +16080,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16133,7 +16142,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16195,34 +16204,34 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
-        <v>7646000</v>
+        <v>6957800</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>22422</v>
+        <v>20404</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>6957860</v>
+        <v>6957800</v>
       </c>
       <c r="L241" s="5" t="n">
         <v>20404</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16650,7 +16659,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16707,34 +16716,34 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
-        <v>8393000</v>
+        <v>7637600</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>21521</v>
+        <v>19584</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>7637630</v>
+        <v>7637600</v>
       </c>
       <c r="L249" s="5" t="n">
         <v>19584</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -16769,7 +16778,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16831,7 +16840,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17413,7 +17422,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17475,7 +17484,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17909,17 +17918,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18292,12 +18301,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $841万
 $24,507/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -18387,20 +18396,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $845万
 $24,991/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $836万
 $24,370/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -18418,12 +18427,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1466万
 $25,056/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18434,20 +18443,20 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$848万
-$24,637/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
+$771万
+$22,419/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $842万
 $24,614/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -18490,12 +18499,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $841万
 $24,885/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -18537,12 +18546,12 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $845万
 $24,552/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -18593,20 +18602,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $838万
 $24,802/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $828万
 $24,146/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -18624,12 +18633,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1440万
 $24,612/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -18640,20 +18649,20 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $839万
 $24,401/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $835万
 $24,427/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -18664,12 +18673,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $838万
 $24,572/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -18696,12 +18705,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $835万
 $24,698/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -18767,12 +18776,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $832万
 $24,405/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -18799,20 +18808,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $831万
 $24,595/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $821万
 $23,939/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -18854,12 +18863,12 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $822万
 $24,038/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -18870,12 +18879,12 @@
 (26年-08月-30日)</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $826万
 $24,220/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -18902,12 +18911,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $828万
 $24,485/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -18957,12 +18966,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $817万
 $23,877/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -19005,12 +19014,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $823万
 $24,358/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -19021,12 +19030,12 @@
 (26年-07月-20日)</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
+      <c r="M14" s="24" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1128万
 $24,055/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19100,20 +19109,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="23" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 390呎 (2房)
-$929万
-$23,810/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="inlineStr">
+$864万
+$22,143/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $819万
 $24,237/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -19139,12 +19148,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1376万
 $23,518/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -19163,12 +19172,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $807万
 $23,602/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -19179,20 +19188,20 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $814万
 $23,883/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $808万
 $23,920/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -19211,12 +19220,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K16" s="24" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $814万
 $24,086/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -19224,7 +19233,7 @@
           <t>L | 343呎 (2房)
 $732万
 $21,336/呎
-(26年-08月-17日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -19290,12 +19299,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$804万
-$23,787/呎
-(已定价未售)</t>
+$748万
+$22,122/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -19314,14 +19323,14 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K17" s="24" t="inlineStr"/>
-      <c r="L17" s="24" t="inlineStr"/>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr"/>
+      <c r="L17" s="25" t="inlineStr"/>
+      <c r="M17" s="24" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1109万
 $23,640/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19403,8 +19412,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="24" t="inlineStr"/>
+      <c r="K18" s="25" t="inlineStr"/>
+      <c r="L18" s="25" t="inlineStr"/>
       <c r="M18" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19492,14 +19501,14 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K19" s="24" t="inlineStr"/>
-      <c r="L19" s="24" t="inlineStr"/>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="K19" s="25" t="inlineStr"/>
+      <c r="L19" s="25" t="inlineStr"/>
+      <c r="M19" s="24" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1101万
 $23,469/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19509,12 +19518,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1357万
 $23,190/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -19554,15 +19563,15 @@
           <t>F | 341呎 (2房)
 $724万
 $21,242/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
+(26年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $790万
 $23,379/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -19581,8 +19590,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr"/>
-      <c r="L20" s="24" t="inlineStr"/>
+      <c r="K20" s="25" t="inlineStr"/>
+      <c r="L20" s="25" t="inlineStr"/>
       <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19646,20 +19655,20 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $784万
 $23,195/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I21" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $876万
 $22,456/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -19670,8 +19679,8 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="K21" s="24" t="inlineStr"/>
-      <c r="L21" s="24" t="inlineStr"/>
+      <c r="K21" s="25" t="inlineStr"/>
+      <c r="L21" s="25" t="inlineStr"/>
       <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19735,38 +19744,38 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$778万
-$23,015/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
+$708万
+$20,943/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $870万
 $22,318/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$881万
-$22,294/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="24" t="inlineStr"/>
-      <c r="M22" s="23" t="inlineStr">
+$801万
+$20,287/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="K22" s="25" t="inlineStr"/>
+      <c r="L22" s="25" t="inlineStr"/>
+      <c r="M22" s="24" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1079万
 $23,002/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19776,12 +19785,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1335万
 $22,824/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -19824,20 +19833,20 @@
 (26年-07月-30日)</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $772万
 $22,852/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $864万
 $22,162/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -19848,8 +19857,8 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="K23" s="24" t="inlineStr"/>
-      <c r="L23" s="24" t="inlineStr"/>
+      <c r="K23" s="25" t="inlineStr"/>
+      <c r="L23" s="25" t="inlineStr"/>
       <c r="M23" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19913,32 +19922,32 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$768万
-$22,722/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
+$699万
+$20,677/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $859万
 $22,015/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
-$867万
-$21,939/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="inlineStr"/>
-      <c r="L24" s="24" t="inlineStr"/>
+$806万
+$20,403/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="K24" s="25" t="inlineStr"/>
+      <c r="L24" s="25" t="inlineStr"/>
       <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19994,28 +20003,28 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$771万
-$22,598/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
+$701万
+$20,564/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$764万
-$22,609/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I25" s="23" t="inlineStr">
+$695万
+$20,575/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $853万
 $21,869/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -20026,14 +20035,14 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="K25" s="24" t="inlineStr"/>
-      <c r="L25" s="24" t="inlineStr"/>
-      <c r="M25" s="23" t="inlineStr">
+      <c r="K25" s="25" t="inlineStr"/>
+      <c r="L25" s="25" t="inlineStr"/>
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1060万
 $22,591/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -20083,28 +20092,28 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$765万
-$22,422/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
+$696万
+$20,404/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $760万
 $22,494/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $846万
 $21,695/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -20115,8 +20124,8 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="24" t="inlineStr"/>
+      <c r="K26" s="25" t="inlineStr"/>
+      <c r="L26" s="25" t="inlineStr"/>
       <c r="M26" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -20172,28 +20181,28 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $758万
 $22,220/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $753万
 $22,272/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
-$839万
-$21,521/呎
-(已定价未售)</t>
+$764万
+$19,584/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -20201,11 +20210,11 @@
           <t>J | 395呎 (2房)
 $774万
 $19,589/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr"/>
-      <c r="L27" s="24" t="inlineStr"/>
+(26年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="K27" s="25" t="inlineStr"/>
+      <c r="L27" s="25" t="inlineStr"/>
       <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -20261,20 +20270,20 @@
 (26年-07月-20日)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $751万
 $22,023/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $745万
 $22,050/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -20293,8 +20302,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K28" s="24" t="inlineStr"/>
-      <c r="L28" s="24" t="inlineStr"/>
+      <c r="K28" s="25" t="inlineStr"/>
+      <c r="L28" s="25" t="inlineStr"/>
       <c r="M28" s="20" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -6486,34 +6486,34 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>8211000</v>
+        <v>7636200</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>23939</v>
+        <v>22263</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>7472010</v>
+        <v>7636200</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>21784</v>
+        <v>22263</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -8084,34 +8084,34 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>8233000</v>
+        <v>7492000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>24358</v>
+        <v>22166</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="5" t="n">
-        <v>7492030</v>
+        <v>7492000</v>
       </c>
       <c r="L113" s="5" t="n">
         <v>22166</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8860,34 +8860,34 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>8192000</v>
+        <v>7454700</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>24237</v>
+        <v>22055</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>7454720</v>
+        <v>7454700</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>22055</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18765,7 +18765,7 @@
           <t>D | 342呎 (2房)
 $770万
 $22,529/呎
-(26年-08月-22日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -18816,12 +18816,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
-$821万
-$23,939/呎
-(在售)</t>
+$764万
+$22,263/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -19014,12 +19014,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
-$823万
-$24,358/呎
-(在售)</t>
+$749万
+$22,166/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -19117,12 +19117,12 @@
 (26年-09月-06日)</t>
         </is>
       </c>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
-$819万
-$24,237/呎
-(在售)</t>
+$745万
+$22,055/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>D | 342呎 (2房)
 $695万
 $20,331/呎
-(26年-08月-24日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -10913,7 +10913,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11544,34 +11544,34 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>11007000</v>
+        <v>10016300</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>23469</v>
+        <v>21357</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="5" t="n">
-        <v>10016370</v>
+        <v>10016300</v>
       </c>
       <c r="L167" s="5" t="n">
         <v>21357</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19369,7 +19369,7 @@
           <t>D | 342呎 (2房)
 $743万
 $21,735/呎
-(26年-08月-23日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -19419,7 +19419,7 @@
           <t>M | 469呎 (2房)
 $1005万
 $21,436/呎
-(26年-08月-25日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -19503,12 +19503,12 @@
       </c>
       <c r="K19" s="25" t="inlineStr"/>
       <c r="L19" s="25" t="inlineStr"/>
-      <c r="M19" s="24" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
-$1101万
-$23,469/呎
-(在售)</t>
+$1002万
+$21,357/呎
+(26年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -19597,7 +19597,7 @@
           <t>M | 469呎 (2房)
 $995万
 $21,225/呎
-(26年-08月-25日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -6168,34 +6168,34 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>8354000</v>
+        <v>7602100</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>24427</v>
+        <v>22228</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>7602140</v>
+        <v>7602100</v>
       </c>
       <c r="L83" s="5" t="n">
         <v>22228</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6230,34 +6230,34 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>8394000</v>
+        <v>7638500</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>24401</v>
+        <v>22205</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>7638540</v>
+        <v>7638500</v>
       </c>
       <c r="L84" s="5" t="n">
         <v>22205</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18649,20 +18649,20 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
-$839万
-$24,401/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
+$764万
+$22,205/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$835万
-$24,427/呎
-(在售)</t>
+$760万
+$22,228/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -18718,7 +18718,7 @@
           <t>L | 343呎 (2房)
 $750万
 $21,861/呎
-(26年-08月-27日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -19130,7 +19130,7 @@
           <t>L | 343呎 (2房)
 $737万
 $21,474/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -19612,7 +19612,7 @@
           <t>A | 585呎 (3房)
 $1229万
 $21,011/呎
-(26年-08月-30日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -7267,7 +7267,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -18924,7 +18924,7 @@
           <t>L | 343呎 (2房)
 $745万
 $21,713/呎
-(26年-08月-25日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -12390,34 +12390,34 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>7902000</v>
+        <v>7190800</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>23379</v>
+        <v>21275</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>7190820</v>
+        <v>7190800</v>
       </c>
       <c r="L180" s="5" t="n">
         <v>21275</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18448,7 +18448,7 @@
           <t>C | 344呎 (2房)
 $771万
 $22,419/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -18512,7 +18512,7 @@
           <t>L | 343呎 (2房)
 $757万
 $22,068/呎
-(26年-08月-30日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -18876,7 +18876,7 @@
           <t>E | 342呎 (2房)
 $749万
 $21,914/呎
-(26年-08月-30日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
@@ -19074,7 +19074,7 @@
           <t>D | 342呎 (2房)
 $739万
 $21,598/呎
-(26年-09月-01日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -19566,12 +19566,12 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="H20" s="24" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$790万
-$23,379/呎
-(在售)</t>
+$719万
+$21,275/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -19765,7 +19765,7 @@
           <t>J | 395呎 (2房)
 $801万
 $20,287/呎
-(26年-09月-06日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="K22" s="25" t="inlineStr"/>
@@ -20008,7 +20008,7 @@
           <t>F | 341呎 (2房)
 $701万
 $20,564/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -20097,7 +20097,7 @@
           <t>F | 341呎 (2房)
 $696万
 $20,404/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -20202,7 +20202,7 @@
           <t>H | 390呎 (2房)
 $764万
 $19,584/呎
-(26年-09月-06日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -3388,34 +3388,34 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>8447000</v>
+        <v>7686700</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>24991</v>
+        <v>22742</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>7686770</v>
+        <v>7686700</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>22742</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9900,34 +9900,34 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>8144000</v>
+        <v>7411000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>23883</v>
+        <v>21733</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>7411040</v>
+        <v>7411000</v>
       </c>
       <c r="L141" s="5" t="n">
         <v>21733</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -13018,23 +13018,23 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>7840000</v>
+        <v>7134400</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>23195</v>
+        <v>21108</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14266,34 +14266,34 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>7724000</v>
+        <v>7028800</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>22852</v>
+        <v>20795</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>7028840</v>
+        <v>7028800</v>
       </c>
       <c r="L210" s="5" t="n">
         <v>20795</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -16142,34 +16142,34 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
-        <v>7603000</v>
+        <v>7298800</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>22494</v>
+        <v>21594</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>6918730</v>
+        <v>7298800</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>20470</v>
+        <v>21594</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -16778,34 +16778,34 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>7528000</v>
+        <v>6850400</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>22272</v>
+        <v>20267</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>6850480</v>
+        <v>6850400</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18396,12 +18396,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
-$845万
-$24,991/呎
-(在售)</t>
+$769万
+$22,742/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="L8" s="24" t="inlineStr">
@@ -19114,7 +19114,7 @@
           <t>J | 390呎 (2房)
 $864万
 $22,143/呎
-(26年-09月-06日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -19188,12 +19188,12 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$814万
-$23,883/呎
-(在售)</t>
+$741万
+$21,733/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -19655,12 +19655,12 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$784万
-$23,195/呎
-(在售)</t>
+$713万
+$21,108/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr">
@@ -19749,7 +19749,7 @@
           <t>G | 338呎 (2房)
 $708万
 $20,943/呎
-(26年-09月-06日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I22" s="24" t="inlineStr">
@@ -19833,12 +19833,12 @@
 (26年-07月-30日)</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$772万
-$22,852/呎
-(在售)</t>
+$703万
+$20,795/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
@@ -19927,7 +19927,7 @@
           <t>G | 338呎 (2房)
 $699万
 $20,677/呎
-(26年-09月-06日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr">
@@ -19943,7 +19943,7 @@
           <t>J | 395呎 (2房)
 $806万
 $20,403/呎
-(26年-09月-06日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="K24" s="25" t="inlineStr"/>
@@ -20100,12 +20100,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="H26" s="24" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$760万
-$22,494/呎
-(在售)</t>
+$730万
+$21,594/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="I26" s="24" t="inlineStr">
@@ -20189,12 +20189,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H27" s="24" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
-$753万
-$22,272/呎
-(在售)</t>
+$685万
+$20,267/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -4188,34 +4188,34 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>8411000</v>
+        <v>7654000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>24885</v>
+        <v>22645</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>7654010</v>
+        <v>7654000</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>22645</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -12956,34 +12956,34 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>8758000</v>
+        <v>7969700</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>22456</v>
+        <v>20435</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>7969780</v>
+        <v>7969700</v>
       </c>
       <c r="L189" s="5" t="n">
         <v>20435</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18499,12 +18499,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
-$841万
-$24,885/呎
-(在售)</t>
+$765万
+$22,645/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -18821,7 +18821,7 @@
           <t>L | 343呎 (2房)
 $764万
 $22,263/呎
-(26年-09月-09日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -19019,7 +19019,7 @@
           <t>K | 338呎 (2房)
 $749万
 $22,166/呎
-(26年-09月-09日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -19122,7 +19122,7 @@
           <t>K | 338呎 (2房)
 $745万
 $22,055/呎
-(26年-09月-07日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -19304,7 +19304,7 @@
           <t>G | 338呎 (2房)
 $748万
 $22,122/呎
-(26年-09月-06日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>M | 469呎 (2房)
 $1002万
 $21,357/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -19663,12 +19663,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
-$876万
-$22,456/呎
-(在售)</t>
+$797万
+$20,435/呎
+(26年-10月-04日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -20016,7 +20016,7 @@
           <t>G | 338呎 (2房)
 $695万
 $20,575/呎
-(26年-09月-06日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -7960,34 +7960,34 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>11282000</v>
+        <v>10266600</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>24055</v>
+        <v>21890</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>10266620</v>
+        <v>10266600</v>
       </c>
       <c r="L111" s="5" t="n">
         <v>21890</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -16840,34 +16840,34 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>7577000</v>
+        <v>6895000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>22220</v>
+        <v>20220</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>6895070</v>
+        <v>6895000</v>
       </c>
       <c r="L251" s="5" t="n">
         <v>20220</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -17484,23 +17484,23 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
-        <v>7510000</v>
+        <v>6834100</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>22023</v>
+        <v>20041</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K261" s="5" t="n">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19030,12 +19030,12 @@
 (26年-07月-20日)</t>
         </is>
       </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
-$1128万
-$24,055/呎
-(在售)</t>
+$1027万
+$21,890/呎
+(26年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -20181,12 +20181,12 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$758万
-$22,220/呎
-(在售)</t>
+$690万
+$20,220/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -20270,12 +20270,12 @@
 (26年-07月-20日)</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$751万
-$22,023/呎
-(在售)</t>
+$683万
+$20,041/呎
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,12 +135,6 @@
       <color rgb="00002060"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -218,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -287,9 +281,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2518,7 +2509,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3326,7 +3317,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4600,7 +4591,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4786,34 +4777,34 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>14658000</v>
+        <v>14071600</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>25056</v>
+        <v>24054</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>13338780</v>
+        <v>14071600</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>22801</v>
+        <v>24054</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -4910,7 +4901,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4972,7 +4963,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -5446,7 +5437,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5772,7 +5763,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -6044,7 +6035,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6173,7 +6164,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6235,7 +6226,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6354,7 +6345,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6548,7 +6539,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6820,7 +6811,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7324,7 +7315,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7588,7 +7579,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7712,7 +7703,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -8480,7 +8471,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -9636,7 +9627,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9838,7 +9829,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10024,7 +10015,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10210,7 +10201,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10272,7 +10263,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -12762,7 +12753,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13452,7 +13443,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13576,7 +13567,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -14204,7 +14195,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14638,7 +14629,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14832,7 +14823,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15336,7 +15327,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15460,7 +15451,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -16080,7 +16071,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -17422,7 +17413,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17918,7 +17909,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17928,12 +17919,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -18301,12 +18292,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $841万
 $24,507/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -18404,12 +18395,12 @@
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $836万
 $24,370/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -18427,12 +18418,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
-$1466万
-$25,056/呎
-(在售)</t>
+$1407万
+$24,054/呎
+(26年-10月-11日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18451,12 +18442,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $842万
 $24,614/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -18546,12 +18537,12 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $845万
 $24,552/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -18602,20 +18593,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $838万
 $24,802/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $828万
 $24,146/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -18633,12 +18624,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1440万
 $24,612/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -18654,7 +18645,7 @@
           <t>C | 344呎 (2房)
 $764万
 $22,205/呎
-(26年-09月-15日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -18662,7 +18653,7 @@
           <t>D | 342呎 (2房)
 $760万
 $22,228/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -18673,12 +18664,12 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $838万
 $24,572/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -18705,12 +18696,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $835万
 $24,698/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -18776,12 +18767,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $832万
 $24,405/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -18808,12 +18799,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $831万
 $24,595/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -18863,12 +18854,12 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $822万
 $24,038/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -18879,12 +18870,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $826万
 $24,220/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -18911,12 +18902,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K13" s="24" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $828万
 $24,485/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -18966,12 +18957,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $817万
 $23,877/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -19148,12 +19139,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1376万
 $23,518/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -19172,12 +19163,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $807万
 $23,602/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -19196,12 +19187,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $808万
 $23,920/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -19220,12 +19211,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>K | 338呎 (2房)
 $814万
 $24,086/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -19323,14 +19314,14 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr"/>
-      <c r="L17" s="25" t="inlineStr"/>
-      <c r="M17" s="24" t="inlineStr">
+      <c r="K17" s="24" t="inlineStr"/>
+      <c r="L17" s="24" t="inlineStr"/>
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1109万
 $23,640/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -19412,8 +19403,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K18" s="25" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr"/>
       <c r="M18" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19501,8 +19492,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="K19" s="25" t="inlineStr"/>
-      <c r="L19" s="25" t="inlineStr"/>
+      <c r="K19" s="24" t="inlineStr"/>
+      <c r="L19" s="24" t="inlineStr"/>
       <c r="M19" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19518,12 +19509,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1357万
 $23,190/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -19590,8 +19581,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K20" s="25" t="inlineStr"/>
-      <c r="L20" s="25" t="inlineStr"/>
+      <c r="K20" s="24" t="inlineStr"/>
+      <c r="L20" s="24" t="inlineStr"/>
       <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19679,8 +19670,8 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="K21" s="25" t="inlineStr"/>
-      <c r="L21" s="25" t="inlineStr"/>
+      <c r="K21" s="24" t="inlineStr"/>
+      <c r="L21" s="24" t="inlineStr"/>
       <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19752,12 +19743,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $870万
 $22,318/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -19768,14 +19759,14 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="K22" s="25" t="inlineStr"/>
-      <c r="L22" s="25" t="inlineStr"/>
-      <c r="M22" s="24" t="inlineStr">
+      <c r="K22" s="24" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1079万
 $23,002/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -19785,12 +19776,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1335万
 $22,824/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -19841,12 +19832,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $864万
 $22,162/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -19857,8 +19848,8 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="K23" s="25" t="inlineStr"/>
-      <c r="L23" s="25" t="inlineStr"/>
+      <c r="K23" s="24" t="inlineStr"/>
+      <c r="L23" s="24" t="inlineStr"/>
       <c r="M23" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -19930,12 +19921,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $859万
 $22,015/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -19946,8 +19937,8 @@
 (26年-09月-25日)</t>
         </is>
       </c>
-      <c r="K24" s="25" t="inlineStr"/>
-      <c r="L24" s="25" t="inlineStr"/>
+      <c r="K24" s="24" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
       <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -20019,12 +20010,12 @@
 (26年-09月-29日)</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $853万
 $21,869/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -20035,14 +20026,14 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="K25" s="25" t="inlineStr"/>
-      <c r="L25" s="25" t="inlineStr"/>
-      <c r="M25" s="24" t="inlineStr">
+      <c r="K25" s="24" t="inlineStr"/>
+      <c r="L25" s="24" t="inlineStr"/>
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1060万
 $22,591/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -20108,12 +20099,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 390呎 (2房)
 $846万
 $21,695/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -20124,8 +20115,8 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="K26" s="25" t="inlineStr"/>
-      <c r="L26" s="25" t="inlineStr"/>
+      <c r="K26" s="24" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr"/>
       <c r="M26" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -20213,8 +20204,8 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr"/>
-      <c r="L27" s="25" t="inlineStr"/>
+      <c r="K27" s="24" t="inlineStr"/>
+      <c r="L27" s="24" t="inlineStr"/>
       <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
@@ -20278,12 +20269,12 @@
 (26年-10月-07日)</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>G | 338呎 (2房)
 $745万
 $22,050/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -20302,8 +20293,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr"/>
-      <c r="L28" s="25" t="inlineStr"/>
+      <c r="K28" s="24" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr"/>
       <c r="M28" s="20" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -19184,7 +19184,7 @@
           <t>F | 341呎 (2房)
 $741万
 $21,733/呎
-(26年-09月-24日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -19562,7 +19562,7 @@
           <t>G | 338呎 (2房)
 $719万
 $21,275/呎
-(26年-09月-22日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -18392,7 +18392,7 @@
           <t>K | 338呎 (2房)
 $769万
 $22,742/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -18495,7 +18495,7 @@
           <t>K | 338呎 (2房)
 $765万
 $22,645/呎
-(26年-10月-01日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -19026,7 +19026,7 @@
           <t>M | 469呎 (2房)
 $1027万
 $21,890/呎
-(26年-10月-05日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
           <t>G | 338呎 (2房)
 $713万
 $21,108/呎
-(26年-09月-24日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>H | 390呎 (2房)
 $797万
 $20,435/呎
-(26年-10月-04日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -19829,7 +19829,7 @@
           <t>G | 338呎 (2房)
 $703万
 $20,795/呎
-(26年-09月-24日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -20096,7 +20096,7 @@
           <t>G | 338呎 (2房)
 $730万
 $21,594/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -20177,7 +20177,7 @@
           <t>F | 341呎 (2房)
 $690万
 $20,220/呎
-(26年-10月-05日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -20185,7 +20185,7 @@
           <t>G | 338呎 (2房)
 $685万
 $20,267/呎
-(26年-09月-24日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
